--- a/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/summary table_Magadan_itog_Selected.xlsx
+++ b/Mussel_Cancer/Mussel_cancer_Magadan_New_Analysis_2025/R_calc_BTN_strategies_2025/Data/summary table_Magadan_itog_Selected.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9324" activeTab="1"/>
+    <workbookView windowWidth="21996" windowHeight="9227" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="table" sheetId="2" r:id="rId1"/>
@@ -868,7 +868,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="966" uniqueCount="151">
   <si>
     <t>Site</t>
   </si>
@@ -1339,6 +1339,9 @@
   </si>
   <si>
     <t>Include</t>
+  </si>
+  <si>
+    <t>NUK-II</t>
   </si>
 </sst>
 </file>
@@ -8090,7 +8093,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:O67"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
@@ -8146,7 +8149,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" hidden="1" spans="1:15">
       <c r="A2" s="2" t="s">
         <v>24</v>
       </c>
@@ -8193,7 +8196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" ht="15.15" spans="1:15">
+    <row r="3" ht="15.15" hidden="1" spans="1:15">
       <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
@@ -8240,7 +8243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="28.8" spans="1:15">
+    <row r="4" ht="28.8" hidden="1" spans="1:15">
       <c r="A4" s="9" t="s">
         <v>31</v>
       </c>
@@ -8287,7 +8290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:15">
+    <row r="5" ht="28.8" hidden="1" spans="1:15">
       <c r="A5" s="10" t="s">
         <v>31</v>
       </c>
@@ -8334,7 +8337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" ht="29.55" spans="1:15">
+    <row r="6" ht="29.55" hidden="1" spans="1:15">
       <c r="A6" s="14" t="s">
         <v>31</v>
       </c>
@@ -8381,7 +8384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" hidden="1" spans="1:15">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -8428,7 +8431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" hidden="1" spans="1:15">
       <c r="A8" s="17" t="s">
         <v>38</v>
       </c>
@@ -8475,7 +8478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="15.15" spans="1:15">
+    <row r="9" ht="15.15" hidden="1" spans="1:15">
       <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
@@ -8522,7 +8525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" ht="28.8" spans="1:15">
+    <row r="10" ht="28.8" hidden="1" spans="1:15">
       <c r="A10" s="9" t="s">
         <v>41</v>
       </c>
@@ -8569,7 +8572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" ht="28.8" spans="1:15">
+    <row r="11" ht="28.8" hidden="1" spans="1:15">
       <c r="A11" s="10" t="s">
         <v>41</v>
       </c>
@@ -8616,7 +8619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="29.55" spans="1:15">
+    <row r="12" ht="29.55" hidden="1" spans="1:15">
       <c r="A12" s="10" t="s">
         <v>41</v>
       </c>
@@ -8663,7 +8666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" ht="28.8" spans="1:15">
+    <row r="13" ht="28.8" hidden="1" spans="1:15">
       <c r="A13" s="9" t="s">
         <v>44</v>
       </c>
@@ -8710,7 +8713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="28.8" spans="1:15">
+    <row r="14" ht="28.8" hidden="1" spans="1:15">
       <c r="A14" s="10" t="s">
         <v>44</v>
       </c>
@@ -8757,7 +8760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" ht="28.8" spans="1:15">
+    <row r="15" ht="28.8" hidden="1" spans="1:15">
       <c r="A15" s="10" t="s">
         <v>44</v>
       </c>
@@ -8804,7 +8807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="29.55" spans="1:15">
+    <row r="16" ht="29.55" hidden="1" spans="1:15">
       <c r="A16" s="14" t="s">
         <v>44</v>
       </c>
@@ -8851,7 +8854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="29.55" spans="1:15">
+    <row r="17" ht="29.55" hidden="1" spans="1:15">
       <c r="A17" s="10" t="s">
         <v>51</v>
       </c>
@@ -8898,7 +8901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="28.8" spans="1:15">
+    <row r="18" ht="29.55" hidden="1" spans="1:15">
       <c r="A18" s="10" t="s">
         <v>51</v>
       </c>
@@ -8945,7 +8948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" ht="28.8" spans="1:15">
+    <row r="19" ht="28.8" hidden="1" spans="1:15">
       <c r="A19" s="10" t="s">
         <v>51</v>
       </c>
@@ -8992,7 +8995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" ht="28.8" spans="1:15">
+    <row r="20" ht="28.8" hidden="1" spans="1:15">
       <c r="A20" s="10" t="s">
         <v>51</v>
       </c>
@@ -9039,7 +9042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="28.8" spans="1:15">
+    <row r="21" ht="28.8" hidden="1" spans="1:15">
       <c r="A21" s="10" t="s">
         <v>51</v>
       </c>
@@ -9086,7 +9089,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="29.55" spans="1:15">
+    <row r="22" ht="29.55" hidden="1" spans="1:15">
       <c r="A22" s="10" t="s">
         <v>51</v>
       </c>
@@ -9133,7 +9136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" ht="29.55" spans="1:15">
+    <row r="23" ht="29.55" hidden="1" spans="1:15">
       <c r="A23" s="29" t="s">
         <v>65</v>
       </c>
@@ -9180,7 +9183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" ht="15.15" spans="1:15">
+    <row r="24" ht="15.15" hidden="1" spans="1:15">
       <c r="A24" s="2" t="s">
         <v>67</v>
       </c>
@@ -9227,7 +9230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" hidden="1" spans="1:15">
       <c r="A25" s="17" t="s">
         <v>67</v>
       </c>
@@ -9274,7 +9277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" hidden="1" spans="1:15">
       <c r="A26" s="17" t="s">
         <v>67</v>
       </c>
@@ -9321,7 +9324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" hidden="1" spans="1:15">
       <c r="A27" s="17" t="s">
         <v>67</v>
       </c>
@@ -9368,7 +9371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" hidden="1" spans="1:15">
       <c r="A28" s="17" t="s">
         <v>67</v>
       </c>
@@ -9415,7 +9418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" hidden="1" spans="1:15">
       <c r="A29" s="17" t="s">
         <v>67</v>
       </c>
@@ -9462,7 +9465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" ht="15.15" spans="1:15">
+    <row r="30" ht="15.15" hidden="1" spans="1:15">
       <c r="A30" s="17" t="s">
         <v>67</v>
       </c>
@@ -9509,7 +9512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" ht="29.55" spans="1:15">
+    <row r="31" ht="29.55" hidden="1" spans="1:15">
       <c r="A31" s="9" t="s">
         <v>78</v>
       </c>
@@ -9556,7 +9559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" ht="29.55" spans="1:15">
+    <row r="32" ht="29.55" hidden="1" spans="1:15">
       <c r="A32" s="14" t="s">
         <v>78</v>
       </c>
@@ -9603,7 +9606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" ht="28.8" spans="1:15">
+    <row r="33" ht="28.8" hidden="1" spans="1:15">
       <c r="A33" s="10" t="s">
         <v>80</v>
       </c>
@@ -9650,7 +9653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" ht="28.8" spans="1:14">
+    <row r="34" ht="28.8" hidden="1" spans="1:14">
       <c r="A34" s="10" t="s">
         <v>80</v>
       </c>
@@ -9694,7 +9697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="28.8" spans="1:15">
+    <row r="35" ht="28.8" hidden="1" spans="1:15">
       <c r="A35" s="10" t="s">
         <v>80</v>
       </c>
@@ -9741,7 +9744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="29.55" spans="1:15">
+    <row r="36" ht="29.55" hidden="1" spans="1:15">
       <c r="A36" s="14" t="s">
         <v>80</v>
       </c>
@@ -9788,7 +9791,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" hidden="1" spans="1:15">
       <c r="A37" s="2" t="s">
         <v>85</v>
       </c>
@@ -9835,7 +9838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" hidden="1" spans="1:15">
       <c r="A38" s="17" t="s">
         <v>85</v>
       </c>
@@ -9882,7 +9885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" ht="15.15" spans="1:15">
+    <row r="39" ht="15.15" hidden="1" spans="1:15">
       <c r="A39" s="17" t="s">
         <v>85</v>
       </c>
@@ -9929,7 +9932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" ht="28.8" spans="1:15">
+    <row r="40" ht="28.8" hidden="1" spans="1:15">
       <c r="A40" s="9" t="s">
         <v>87</v>
       </c>
@@ -9976,7 +9979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" ht="28.8" spans="1:15">
+    <row r="41" ht="28.8" hidden="1" spans="1:15">
       <c r="A41" s="10" t="s">
         <v>87</v>
       </c>
@@ -10023,7 +10026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" ht="28.8" spans="1:15">
+    <row r="42" ht="28.8" hidden="1" spans="1:15">
       <c r="A42" s="10" t="s">
         <v>87</v>
       </c>
@@ -10070,7 +10073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" ht="29.55" spans="1:15">
+    <row r="43" ht="29.55" hidden="1" spans="1:15">
       <c r="A43" s="14" t="s">
         <v>87</v>
       </c>
@@ -10117,12 +10120,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="29.55" spans="1:15">
+    <row r="44" ht="28.8" spans="1:15">
       <c r="A44" s="29" t="s">
         <v>91</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="C44" s="31">
         <v>59.577677</v>
@@ -10164,7 +10167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
+    <row r="45" hidden="1" spans="1:15">
       <c r="A45" s="17" t="s">
         <v>95</v>
       </c>
@@ -10211,7 +10214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" hidden="1" spans="1:15">
       <c r="A46" s="17" t="s">
         <v>95</v>
       </c>
@@ -10258,7 +10261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" ht="15.15" spans="1:15">
+    <row r="47" ht="15.15" hidden="1" spans="1:15">
       <c r="A47" s="6" t="s">
         <v>95</v>
       </c>
@@ -10305,7 +10308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" ht="15.15" spans="1:15">
+    <row r="48" ht="15.15" hidden="1" spans="1:15">
       <c r="A48" s="2" t="s">
         <v>101</v>
       </c>
@@ -10352,7 +10355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" hidden="1" spans="1:15">
       <c r="A49" s="17" t="s">
         <v>101</v>
       </c>
@@ -10399,7 +10402,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" ht="15.15" spans="1:15">
+    <row r="50" ht="15.15" hidden="1" spans="1:15">
       <c r="A50" s="6" t="s">
         <v>101</v>
       </c>
@@ -10446,7 +10449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" ht="43.2" spans="1:15">
+    <row r="51" ht="43.2" hidden="1" spans="1:15">
       <c r="A51" s="9" t="s">
         <v>108</v>
       </c>
@@ -10493,7 +10496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" ht="43.2" spans="1:15">
+    <row r="52" ht="43.2" hidden="1" spans="1:15">
       <c r="A52" s="10" t="s">
         <v>108</v>
       </c>
@@ -10540,7 +10543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" ht="43.95" spans="1:15">
+    <row r="53" ht="43.95" hidden="1" spans="1:15">
       <c r="A53" s="14" t="s">
         <v>108</v>
       </c>
@@ -10587,7 +10590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" hidden="1" spans="1:15">
       <c r="A54" s="2" t="s">
         <v>115</v>
       </c>
@@ -10634,7 +10637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" hidden="1" spans="1:15">
       <c r="A55" s="17" t="s">
         <v>115</v>
       </c>
@@ -10681,7 +10684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" ht="15.15" hidden="1" spans="1:15">
       <c r="A56" s="6" t="s">
         <v>115</v>
       </c>
@@ -10728,7 +10731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" ht="28.8" spans="1:15">
+    <row r="57" ht="28.8" hidden="1" spans="1:15">
       <c r="A57" s="9" t="s">
         <v>122</v>
       </c>
@@ -10775,7 +10778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" ht="28.8" spans="1:15">
+    <row r="58" ht="28.8" hidden="1" spans="1:15">
       <c r="A58" s="10" t="s">
         <v>122</v>
       </c>
@@ -10822,7 +10825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" ht="29.55" spans="1:14">
+    <row r="59" ht="29.55" hidden="1" spans="1:14">
       <c r="A59" s="10" t="s">
         <v>122</v>
       </c>
@@ -10866,7 +10869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" ht="15.15" spans="1:15">
+    <row r="60" ht="15.15" hidden="1" spans="1:15">
       <c r="A60" s="2" t="s">
         <v>130</v>
       </c>
@@ -10913,7 +10916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" ht="15.15" spans="1:15">
+    <row r="61" ht="15.15" hidden="1" spans="1:15">
       <c r="A61" s="17" t="s">
         <v>130</v>
       </c>
@@ -10960,7 +10963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:15">
+    <row r="62" hidden="1" spans="1:15">
       <c r="A62" s="17" t="s">
         <v>130</v>
       </c>
@@ -11007,7 +11010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:15">
+    <row r="63" hidden="1" spans="1:15">
       <c r="A63" s="17" t="s">
         <v>130</v>
       </c>
@@ -11054,7 +11057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:15">
+    <row r="64" hidden="1" spans="1:15">
       <c r="A64" s="17" t="s">
         <v>130</v>
       </c>
@@ -11101,7 +11104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" ht="15.15" spans="1:15">
+    <row r="65" ht="15.15" hidden="1" spans="1:15">
       <c r="A65" s="6" t="s">
         <v>130</v>
       </c>
@@ -11148,7 +11151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" ht="29.55" spans="1:15">
+    <row r="66" ht="29.55" hidden="1" spans="1:15">
       <c r="A66" s="29" t="s">
         <v>140</v>
       </c>
@@ -11195,7 +11198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" ht="15.15" spans="1:15">
+    <row r="67" ht="15.15" hidden="1" spans="1:15">
       <c r="A67" s="104" t="s">
         <v>142</v>
       </c>
@@ -11244,6 +11247,11 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:O67" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="NUK_II"/>
+      </filters>
+    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
